--- a/data/downloads/B8RzotP15G9BgVCqIl3lCbOd.xlsx
+++ b/data/downloads/B8RzotP15G9BgVCqIl3lCbOd.xlsx
@@ -710,7 +710,7 @@
       <c r="A33" s="1" t="inlineStr"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>This does not replace your care team: it is a decision-support model for interpreting this document's own evidence, not a diagnosis or an individual treatment plan.</t>
+          <t>This does not replace your care team: it is a what-if model for interpreting this document's own evidence, not a diagnosis or an individual treatment plan.</t>
         </is>
       </c>
     </row>

--- a/data/downloads/B8RzotP15G9BgVCqIl3lCbOd.xlsx
+++ b/data/downloads/B8RzotP15G9BgVCqIl3lCbOd.xlsx
@@ -965,7 +965,7 @@
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>Payer unclear</t>
+          <t>Payer not stated in the paper</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t>Payer unclear</t>
+          <t>Payer not stated in the paper</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>Payer unclear</t>
+          <t>Payer not stated in the paper</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>Payer unclear</t>
+          <t>Payer not stated in the paper</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>Payer unclear</t>
+          <t>Payer not stated in the paper</t>
         </is>
       </c>
     </row>
